--- a/Stock Daily 2026-09-22.xlsx
+++ b/Stock Daily 2026-09-22.xlsx
@@ -7343,16 +7343,28 @@
       <c r="A4" s="121" t="n">
         <v>2026</v>
       </c>
-      <c r="B4" s="122" t="n"/>
-      <c r="C4" s="122" t="n"/>
-      <c r="D4" s="122" t="n"/>
+      <c r="B4" s="122" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="122" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" s="118" t="n"/>
       <c r="F4" s="122" t="n">
         <v>2026</v>
       </c>
-      <c r="G4" s="122" t="n"/>
-      <c r="H4" s="122" t="n"/>
-      <c r="I4" s="122" t="n"/>
+      <c r="G4" s="122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="122" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" s="120" t="n"/>
       <c r="K4" s="120" t="n"/>
       <c r="L4" s="120" t="n"/>
@@ -7365,8 +7377,12 @@
       <c r="B5" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="123" t="n"/>
-      <c r="D5" s="123" t="n"/>
+      <c r="C5" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="123" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" s="118" t="n"/>
       <c r="F5" s="122" t="n">
         <v>2025</v>
@@ -7374,8 +7390,12 @@
       <c r="G5" s="123" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="123" t="n"/>
-      <c r="I5" s="123" t="n"/>
+      <c r="H5" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="123" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" s="120" t="n"/>
       <c r="K5" s="120" t="n"/>
       <c r="L5" s="120" t="n"/>
@@ -7385,16 +7405,28 @@
       <c r="A6" s="122" t="n">
         <v>2024</v>
       </c>
-      <c r="B6" s="123" t="n"/>
-      <c r="C6" s="123" t="n"/>
-      <c r="D6" s="123" t="n"/>
+      <c r="B6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="123" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" s="118" t="n"/>
       <c r="F6" s="122" t="n">
         <v>2024</v>
       </c>
-      <c r="G6" s="123" t="n"/>
-      <c r="H6" s="123" t="n"/>
-      <c r="I6" s="123" t="n"/>
+      <c r="G6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="16.15" customHeight="1">
       <c r="A7" s="124" t="n">
@@ -7403,8 +7435,12 @@
       <c r="B7" s="125" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="125" t="n"/>
-      <c r="D7" s="125" t="n"/>
+      <c r="C7" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="125" t="n">
+        <v>0</v>
+      </c>
       <c r="E7" s="111" t="n"/>
       <c r="F7" s="124" t="n">
         <v>2023</v>
@@ -7412,22 +7448,38 @@
       <c r="G7" s="125" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="125" t="n"/>
-      <c r="I7" s="125" t="n"/>
+      <c r="H7" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="16.15" customHeight="1" thickBot="1">
       <c r="A8" s="124" t="n">
         <v>2022</v>
       </c>
-      <c r="B8" s="125" t="n"/>
-      <c r="C8" s="125" t="n"/>
-      <c r="D8" s="125" t="n"/>
+      <c r="B8" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="125" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" s="124" t="n">
         <v>2022</v>
       </c>
-      <c r="G8" s="125" t="n"/>
-      <c r="H8" s="125" t="n"/>
-      <c r="I8" s="125" t="n"/>
+      <c r="G8" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="16.15" customHeight="1" thickTop="1">
       <c r="A9" s="124" t="n">
@@ -7436,16 +7488,24 @@
       <c r="B9" s="125" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="125" t="n"/>
-      <c r="D9" s="125" t="n"/>
+      <c r="C9" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="125" t="n">
+        <v>0</v>
+      </c>
       <c r="F9" s="124" t="n">
         <v>2021</v>
       </c>
       <c r="G9" s="125" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="125" t="n"/>
-      <c r="I9" s="125" t="n"/>
+      <c r="H9" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="124" t="n">
@@ -7454,16 +7514,24 @@
       <c r="B10" s="125" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="125" t="n"/>
-      <c r="D10" s="125" t="n"/>
+      <c r="C10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="125" t="n">
+        <v>0</v>
+      </c>
       <c r="F10" s="124" t="n">
         <v>2020</v>
       </c>
       <c r="G10" s="125" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="125" t="n"/>
-      <c r="I10" s="125" t="n"/>
+      <c r="H10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="126" t="inlineStr">

--- a/Stock Daily 2026-09-22.xlsx
+++ b/Stock Daily 2026-09-22.xlsx
@@ -7068,8 +7068,8 @@
   <mergeCells count="46">
     <mergeCell ref="V55:W55"/>
     <mergeCell ref="W59:AO59"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="AG2:AL2"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A2:B3"/>
     <mergeCell ref="W58:AO58"/>
     <mergeCell ref="I43:K43"/>
@@ -7216,7 +7216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.15" customHeight="1"/>
   <cols>
     <col width="5.75" bestFit="1" customWidth="1" style="96" min="1" max="1"/>
@@ -7340,237 +7340,122 @@
       <c r="M3" s="120" t="n"/>
     </row>
     <row r="4" ht="16.15" customHeight="1">
-      <c r="A4" s="121" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="122" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="122" t="n">
-        <v>0</v>
-      </c>
+      <c r="A4" s="122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="123" t="n"/>
+      <c r="D4" s="123" t="n"/>
       <c r="E4" s="118" t="n"/>
       <c r="F4" s="122" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G4" s="122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="122" t="n">
-        <v>0</v>
-      </c>
+        <v>2025</v>
+      </c>
+      <c r="G4" s="123" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" s="123" t="n"/>
+      <c r="I4" s="123" t="n"/>
       <c r="J4" s="120" t="n"/>
       <c r="K4" s="120" t="n"/>
       <c r="L4" s="120" t="n"/>
       <c r="M4" s="120" t="n"/>
     </row>
     <row r="5" ht="16.15" customHeight="1">
-      <c r="A5" s="122" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="123" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="118" t="n"/>
-      <c r="F5" s="122" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G5" s="123" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="120" t="n"/>
-      <c r="K5" s="120" t="n"/>
-      <c r="L5" s="120" t="n"/>
-      <c r="M5" s="120" t="n"/>
+      <c r="A5" s="124" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="125" t="n"/>
+      <c r="D5" s="125" t="n"/>
+      <c r="E5" s="111" t="n"/>
+      <c r="F5" s="124" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G5" s="125" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="125" t="n"/>
+      <c r="I5" s="125" t="n"/>
     </row>
     <row r="6" ht="16.15" customHeight="1">
-      <c r="A6" s="122" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="118" t="n"/>
-      <c r="F6" s="122" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="123" t="n">
-        <v>0</v>
-      </c>
+      <c r="A6" s="124" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B6" s="125" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="125" t="n"/>
+      <c r="D6" s="125" t="n"/>
+      <c r="F6" s="124" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G6" s="125" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="125" t="n"/>
+      <c r="I6" s="125" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1">
       <c r="A7" s="124" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B7" s="125" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="111" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C7" s="125" t="n"/>
+      <c r="D7" s="125" t="n"/>
       <c r="F7" s="124" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="G7" s="125" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="125" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H7" s="125" t="n"/>
+      <c r="I7" s="125" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" thickBot="1">
-      <c r="A8" s="124" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B8" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="124" t="n">
-        <v>2022</v>
-      </c>
-      <c r="G8" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="16.15" customHeight="1" thickTop="1">
-      <c r="A9" s="124" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B9" s="125" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="124" t="n">
-        <v>2021</v>
-      </c>
-      <c r="G9" s="125" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="124" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B10" s="125" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="124" t="n">
-        <v>2020</v>
-      </c>
-      <c r="G10" s="125" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="126" t="inlineStr">
+      <c r="A8" s="126" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="127">
-        <f>SUM(B4:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="127">
-        <f>SUM(C4:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="127">
-        <f>SUM(D4:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="128" t="n"/>
-      <c r="F11" s="126" t="inlineStr">
+      <c r="B8" s="127">
+        <f>SUM(B4:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="127">
+        <f>SUM(C4:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="127">
+        <f>SUM(D4:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="128" t="n"/>
+      <c r="F8" s="126" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G11" s="127">
-        <f>SUM(G4:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="127">
-        <f>SUM(H4:H10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="127">
-        <f>SUM(I4:I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="129" t="n"/>
-    </row>
+      <c r="G8" s="127">
+        <f>SUM(G4:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="127">
+        <f>SUM(H4:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="127">
+        <f>SUM(I4:I7)</f>
+        <v/>
+      </c>
+      <c r="J8" s="129" t="n"/>
+    </row>
+    <row r="9" ht="16.15" customHeight="1" thickTop="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
